--- a/EXPORTS/Mldata_Preprocessed.xlsx
+++ b/EXPORTS/Mldata_Preprocessed.xlsx
@@ -487,29 +487,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -524,29 +522,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -561,29 +557,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>0.6140350877192982</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -598,29 +592,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>0.9649122807017545</v>
       </c>
       <c r="G5" t="n">
-        <v>54</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -635,29 +627,27 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -672,29 +662,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -709,29 +697,27 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -746,29 +732,27 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -783,29 +767,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -820,29 +802,27 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>0.4067796610169491</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -857,29 +837,27 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -894,29 +872,27 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -931,29 +907,27 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>0.9827586206896551</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -968,29 +942,27 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1005,29 +977,27 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>0.6779661016949153</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="G16" t="n">
-        <v>45</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1042,29 +1012,27 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G17" t="n">
-        <v>36</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,29 +1047,27 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>0.6551724137931035</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1116,29 +1082,27 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>0.4067796610169491</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="G19" t="n">
-        <v>28</v>
+        <v>0.4181818181818181</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1153,29 +1117,27 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>0.95</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>0.9661016949152543</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>0.9298245614035088</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1190,29 +1152,27 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="E21" t="n">
-        <v>45</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="G21" t="n">
-        <v>45</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1227,29 +1187,27 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1264,29 +1222,27 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>0.9661016949152543</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="G23" t="n">
-        <v>43.06349206349206</v>
+        <v>0.6920634920634919</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1301,29 +1257,27 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>0.8245614035087718</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1338,29 +1292,27 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="G25" t="n">
-        <v>42</v>
+        <v>0.6727272727272726</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1375,29 +1327,27 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1412,29 +1362,27 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="G27" t="n">
-        <v>29</v>
+        <v>0.4363636363636363</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+      <c r="I27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1449,29 +1397,27 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1486,29 +1432,27 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>33</v>
+        <v>0.55</v>
       </c>
       <c r="D29" t="n">
-        <v>42.921875</v>
+        <v>0.7105402542372882</v>
       </c>
       <c r="E29" t="n">
-        <v>56</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="F29" t="n">
-        <v>43.1875</v>
+        <v>0.7050438596491229</v>
       </c>
       <c r="G29" t="n">
-        <v>48</v>
+        <v>0.7818181818181817</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1523,29 +1467,27 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>0.8245614035087718</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1560,29 +1502,27 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1597,29 +1537,27 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1634,29 +1572,27 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>0.7627118644067797</v>
       </c>
       <c r="E33" t="n">
-        <v>47</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="F33" t="n">
-        <v>48</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G33" t="n">
-        <v>49</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1671,29 +1607,27 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>0.6551724137931035</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1708,29 +1642,27 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>0.9661016949152543</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="G35" t="n">
-        <v>55</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1745,29 +1677,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>58</v>
+        <v>0.9649122807017545</v>
       </c>
       <c r="G36" t="n">
-        <v>57</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1782,29 +1712,27 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>54</v>
+        <v>0.9</v>
       </c>
       <c r="D37" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="F37" t="n">
-        <v>54</v>
+        <v>0.8947368421052631</v>
       </c>
       <c r="G37" t="n">
-        <v>52</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1819,29 +1747,27 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54</v>
+        <v>0.9</v>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E38" t="n">
-        <v>56</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="F38" t="n">
-        <v>57</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>0.9636363636363635</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1856,29 +1782,27 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>0.1896551724137931</v>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+      <c r="I39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1893,29 +1817,27 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1930,29 +1852,27 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1970,26 +1890,24 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>43.06349206349206</v>
+        <v>0.6920634920634919</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+      <c r="I42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2004,29 +1922,27 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2041,29 +1957,27 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F44" t="n">
-        <v>35</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="G44" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2078,29 +1992,27 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D45" t="n">
-        <v>35</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="E45" t="n">
-        <v>35</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="F45" t="n">
-        <v>35</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2115,29 +2027,27 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>59</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E46" t="n">
-        <v>59</v>
+        <v>0.9827586206896551</v>
       </c>
       <c r="F46" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2152,29 +2062,27 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D47" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E47" t="n">
-        <v>40</v>
+        <v>0.6551724137931035</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G47" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2189,29 +2097,27 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E48" t="n">
-        <v>55</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="F48" t="n">
-        <v>55</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="G48" t="n">
-        <v>55</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2226,29 +2132,27 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>58</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>59</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2263,29 +2167,27 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>42.33846153846154</v>
+        <v>0.7056410256410256</v>
       </c>
       <c r="D50" t="n">
-        <v>42.921875</v>
+        <v>0.7105402542372882</v>
       </c>
       <c r="E50" t="n">
-        <v>42.86153846153846</v>
+        <v>0.7045092838196286</v>
       </c>
       <c r="F50" t="n">
-        <v>43.1875</v>
+        <v>0.7050438596491229</v>
       </c>
       <c r="G50" t="n">
-        <v>43.06349206349206</v>
+        <v>0.6920634920634919</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2300,29 +2202,27 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>59</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2337,29 +2237,27 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E52" t="n">
-        <v>45</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G52" t="n">
-        <v>40</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2374,29 +2272,27 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>42.33846153846154</v>
+        <v>0.7056410256410256</v>
       </c>
       <c r="D53" t="n">
-        <v>42.921875</v>
+        <v>0.7105402542372882</v>
       </c>
       <c r="E53" t="n">
-        <v>42.86153846153846</v>
+        <v>0.7045092838196286</v>
       </c>
       <c r="F53" t="n">
-        <v>43.1875</v>
+        <v>0.7050438596491229</v>
       </c>
       <c r="G53" t="n">
-        <v>43.06349206349206</v>
+        <v>0.6920634920634919</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2411,29 +2307,27 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D54" t="n">
-        <v>45</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="F54" t="n">
-        <v>45</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="G54" t="n">
-        <v>50</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2448,29 +2342,27 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>49</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>0.8135593220338984</v>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>0.810344827586207</v>
       </c>
       <c r="F55" t="n">
-        <v>49</v>
+        <v>0.8070175438596492</v>
       </c>
       <c r="G55" t="n">
-        <v>49</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2485,29 +2377,27 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D56" t="n">
-        <v>56</v>
+        <v>0.9322033898305085</v>
       </c>
       <c r="E56" t="n">
-        <v>57</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="F56" t="n">
-        <v>58</v>
+        <v>0.9649122807017545</v>
       </c>
       <c r="G56" t="n">
-        <v>59</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2522,29 +2412,27 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D57" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F57" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2559,29 +2447,27 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D58" t="n">
-        <v>46</v>
+        <v>0.7627118644067797</v>
       </c>
       <c r="E58" t="n">
-        <v>43</v>
+        <v>0.706896551724138</v>
       </c>
       <c r="F58" t="n">
-        <v>39</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G58" t="n">
-        <v>39</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2596,29 +2482,27 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="E59" t="n">
-        <v>35</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="F59" t="n">
-        <v>35</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="G59" t="n">
-        <v>35</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2633,29 +2517,27 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E60" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F60" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G60" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2670,29 +2552,27 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>55</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E61" t="n">
-        <v>55</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="F61" t="n">
-        <v>55</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="G61" t="n">
-        <v>55</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2707,29 +2587,27 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D62" t="n">
-        <v>42</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="F62" t="n">
-        <v>43</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="G62" t="n">
-        <v>50</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2744,29 +2622,27 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="E63" t="n">
-        <v>48</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="F63" t="n">
-        <v>52</v>
+        <v>0.8596491228070176</v>
       </c>
       <c r="G63" t="n">
-        <v>50</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2781,29 +2657,27 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>40</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>0.4035087719298245</v>
       </c>
       <c r="G64" t="n">
-        <v>28</v>
+        <v>0.4181818181818181</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2818,29 +2692,27 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>24</v>
+        <v>0.4</v>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>0.4067796610169491</v>
       </c>
       <c r="E65" t="n">
-        <v>26</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="G65" t="n">
-        <v>24</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2855,29 +2727,27 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E66" t="n">
-        <v>30</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="G66" t="n">
-        <v>30</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2892,29 +2762,27 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>45</v>
+        <v>0.75</v>
       </c>
       <c r="D67" t="n">
-        <v>40</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="F67" t="n">
-        <v>48</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G67" t="n">
-        <v>46</v>
+        <v>0.7454545454545454</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2929,29 +2797,27 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>35</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="E68" t="n">
-        <v>40</v>
+        <v>0.6551724137931035</v>
       </c>
       <c r="F68" t="n">
-        <v>45</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="G68" t="n">
-        <v>48</v>
+        <v>0.7818181818181817</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="I68" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
